--- a/Stock_Analysis_Master.xlsx
+++ b/Stock_Analysis_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/casperkangas/Documents/VS Code/Personal Projects/nordnet-scraper/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DB33A40-0E82-FB43-BE93-731DEBD93FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4885804F-193F-DD43-A1D8-18A2C329F40D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="68800" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>Ticker</t>
   </si>
@@ -28,6 +28,9 @@
     <t>Date</t>
   </si>
   <si>
+    <t>Industry</t>
+  </si>
+  <si>
     <t>Liikevaihto</t>
   </si>
   <si>
@@ -73,49 +76,43 @@
     <t>Analyst Rating</t>
   </si>
   <si>
-    <t>EPS Score</t>
-  </si>
-  <si>
-    <t>Osinkotuotto Score</t>
-  </si>
-  <si>
-    <t>Liikevaihto Score</t>
-  </si>
-  <si>
-    <t>EBIT Score</t>
-  </si>
-  <si>
-    <t>Omistajia Nordnetissä* Score</t>
-  </si>
-  <si>
-    <t>Analyst Rating Score</t>
-  </si>
-  <si>
-    <t>P/E Score</t>
-  </si>
-  <si>
-    <t>P/B Score</t>
-  </si>
-  <si>
-    <t>PEG Score</t>
-  </si>
-  <si>
-    <t>P/S Score</t>
-  </si>
-  <si>
     <t>Total Value Score</t>
   </si>
   <si>
+    <t>Industry Value Score</t>
+  </si>
+  <si>
     <t>NDA FI</t>
   </si>
   <si>
     <t>2026-03-28</t>
   </si>
   <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>AKTIA</t>
+  </si>
+  <si>
+    <t>OMASP</t>
+  </si>
+  <si>
+    <t>MANTA</t>
+  </si>
+  <si>
+    <t>NOKIA</t>
+  </si>
+  <si>
+    <t>Tech</t>
+  </si>
+  <si>
+    <t>QTCOM</t>
+  </si>
+  <si>
     <t>KEMPOWR</t>
   </si>
   <si>
-    <t>NOKIA</t>
+    <t>Industrial</t>
   </si>
   <si>
     <t>POSTI</t>
@@ -146,7 +143,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,22 +152,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF15904C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEE28F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9EF8B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF191"/>
+        <fgColor rgb="FF39A758"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F397"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEBC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F295"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF1A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEC877"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1EC86"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BA62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF08D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F59D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FAA59"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFE47A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BBF64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF36A657"/>
       </patternFill>
     </fill>
   </fills>
@@ -186,12 +233,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,36 +551,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB5"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="3.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -584,331 +635,459 @@
       <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="D2">
+        <v>25534000000</v>
+      </c>
+      <c r="F2">
+        <v>1.3937999999999999</v>
+      </c>
+      <c r="G2">
+        <v>0.96</v>
+      </c>
+      <c r="H2">
+        <v>6.5780265920223897</v>
+      </c>
+      <c r="I2">
+        <v>10.2525469938298</v>
+      </c>
+      <c r="J2">
+        <v>1.5074396206611</v>
+      </c>
+      <c r="K2">
+        <v>2.0625246000000002</v>
+      </c>
+      <c r="L2">
+        <v>1.9352557374481101</v>
+      </c>
+      <c r="M2">
+        <v>112509</v>
+      </c>
+      <c r="N2">
+        <v>16</v>
+      </c>
+      <c r="O2">
+        <v>6</v>
+      </c>
+      <c r="P2">
+        <v>4</v>
+      </c>
+      <c r="Q2">
+        <v>26</v>
+      </c>
+      <c r="R2">
+        <v>3.9230769230769229</v>
+      </c>
+      <c r="S2" s="1">
+        <v>85.91</v>
+      </c>
+      <c r="T2" s="2">
+        <v>80.56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2">
-        <v>25534000000</v>
-      </c>
-      <c r="E2">
-        <v>1.3937999999999999</v>
-      </c>
-      <c r="F2">
-        <v>0.96</v>
-      </c>
-      <c r="G2">
-        <v>6.5780265920223897</v>
-      </c>
-      <c r="H2">
-        <v>10.2525469938298</v>
-      </c>
-      <c r="I2">
-        <v>1.5074396206611</v>
-      </c>
-      <c r="J2">
-        <v>2.0625246000000002</v>
-      </c>
-      <c r="K2">
-        <v>1.9352557374481101</v>
-      </c>
-      <c r="L2">
-        <v>112509</v>
-      </c>
-      <c r="M2">
-        <v>16</v>
-      </c>
-      <c r="N2">
-        <v>6</v>
-      </c>
-      <c r="O2">
-        <v>4</v>
-      </c>
-      <c r="P2">
-        <v>26</v>
-      </c>
-      <c r="Q2">
-        <v>3.9230769230769229</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
-      <c r="V2">
-        <v>1</v>
-      </c>
-      <c r="W2">
-        <v>1</v>
-      </c>
-      <c r="X2">
-        <v>1</v>
-      </c>
-      <c r="Y2">
-        <v>0.75</v>
-      </c>
-      <c r="Z2">
-        <v>1</v>
-      </c>
-      <c r="AA2">
-        <v>0.5</v>
-      </c>
-      <c r="AB2" s="1">
-        <v>91.67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3">
+        <v>817274000</v>
+      </c>
+      <c r="F3">
+        <v>0.14030000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="H3">
+        <v>6.4566929133858304</v>
       </c>
       <c r="I3">
-        <v>6.8066413682871403</v>
+        <v>90.520313613684905</v>
       </c>
       <c r="J3">
-        <v>35.659064999999998</v>
-      </c>
-      <c r="K3">
-        <v>2.75783118188044</v>
+        <v>1.4410562601980299</v>
       </c>
       <c r="L3">
-        <v>29523</v>
+        <v>1.1368052237071</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>10393</v>
       </c>
       <c r="N3">
         <v>2</v>
       </c>
       <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+      <c r="R3">
+        <v>5</v>
+      </c>
+      <c r="S3" s="3">
+        <v>57.59</v>
+      </c>
+      <c r="T3" s="4">
+        <v>59.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4">
+        <v>332541000</v>
+      </c>
+      <c r="F4">
+        <v>1.1898</v>
+      </c>
+      <c r="G4">
+        <v>0.36</v>
+      </c>
+      <c r="H4">
+        <v>3.0150753768844201</v>
+      </c>
+      <c r="I4">
+        <v>10.035300050428599</v>
+      </c>
+      <c r="J4">
+        <v>0.64066139435606295</v>
+      </c>
+      <c r="L4">
+        <v>1.2012772835607599</v>
+      </c>
+      <c r="M4">
+        <v>4456</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>1</v>
       </c>
-      <c r="P3">
-        <v>7</v>
-      </c>
-      <c r="Q3">
-        <v>3.8571428571428572</v>
-      </c>
-      <c r="S3">
-        <v>0.375</v>
-      </c>
-      <c r="V3">
-        <v>0.5</v>
-      </c>
-      <c r="W3">
-        <v>0.75</v>
-      </c>
-      <c r="Y3">
-        <v>0.25</v>
-      </c>
-      <c r="Z3">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="AA3">
-        <v>0.25</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>40.97</v>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4" s="3">
+        <v>57.81</v>
+      </c>
+      <c r="T4" s="5">
+        <v>56.25</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4">
-        <v>19889000000</v>
-      </c>
-      <c r="D4">
-        <v>1647000000</v>
-      </c>
-      <c r="E4">
-        <v>0.11609999999999999</v>
-      </c>
-      <c r="G4">
-        <v>2.0390329158170699</v>
-      </c>
-      <c r="H4">
-        <v>59.138673557278203</v>
-      </c>
-      <c r="I4">
-        <v>1.8280961281424599</v>
-      </c>
-      <c r="J4">
-        <v>3.1925037000000001</v>
-      </c>
-      <c r="K4">
-        <v>1.8996481075971601</v>
-      </c>
-      <c r="L4">
-        <v>69675</v>
-      </c>
-      <c r="M4">
-        <v>14</v>
-      </c>
-      <c r="N4">
-        <v>13</v>
-      </c>
-      <c r="O4">
-        <v>7</v>
-      </c>
-      <c r="P4">
-        <v>34</v>
-      </c>
-      <c r="Q4">
-        <v>3.4117647058823528</v>
-      </c>
-      <c r="R4">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="S4">
-        <v>0.75</v>
-      </c>
-      <c r="T4">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="U4">
-        <v>1</v>
-      </c>
-      <c r="V4">
-        <v>0.75</v>
-      </c>
-      <c r="W4">
-        <v>0.25</v>
-      </c>
-      <c r="X4">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="Y4">
-        <v>0.5</v>
-      </c>
-      <c r="Z4">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="AA4">
-        <v>0.75</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <v>1447600000</v>
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
       </c>
       <c r="D5">
-        <v>48700000</v>
-      </c>
-      <c r="E5">
-        <v>0.58020000000000005</v>
+        <v>1268600000</v>
       </c>
       <c r="F5">
-        <v>0.84</v>
+        <v>0.31030000000000002</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="H5">
-        <v>15.4360565322303</v>
+        <v>9.7575399172087494</v>
       </c>
       <c r="I5">
-        <v>1.3099235926658299</v>
-      </c>
-      <c r="K5">
-        <v>0.25056507322464799</v>
+        <v>21.7982597486304</v>
+      </c>
+      <c r="J5">
+        <v>2.3791183474202202</v>
       </c>
       <c r="L5">
-        <v>7103</v>
+        <v>2.6859898225035499</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>84564</v>
       </c>
       <c r="N5">
         <v>2</v>
       </c>
       <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>5</v>
+      </c>
+      <c r="Q5">
+        <v>8</v>
+      </c>
+      <c r="R5">
+        <v>2.25</v>
+      </c>
+      <c r="S5" s="6">
+        <v>50.67</v>
+      </c>
+      <c r="T5" s="5">
+        <v>56.25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6">
+        <v>19889000000</v>
+      </c>
+      <c r="E6">
+        <v>1647000000</v>
+      </c>
+      <c r="F6">
+        <v>0.11609999999999999</v>
+      </c>
+      <c r="H6">
+        <v>2.0390329158170699</v>
+      </c>
+      <c r="I6">
+        <v>59.138673557278203</v>
+      </c>
+      <c r="J6">
+        <v>1.8280961281424599</v>
+      </c>
+      <c r="K6">
+        <v>3.1925037000000001</v>
+      </c>
+      <c r="L6">
+        <v>1.8996481075971601</v>
+      </c>
+      <c r="M6">
+        <v>69675</v>
+      </c>
+      <c r="N6">
+        <v>14</v>
+      </c>
+      <c r="O6">
+        <v>13</v>
+      </c>
+      <c r="P6">
+        <v>7</v>
+      </c>
+      <c r="Q6">
+        <v>34</v>
+      </c>
+      <c r="R6">
+        <v>3.4117647058823528</v>
+      </c>
+      <c r="S6" s="7">
+        <v>57.86</v>
+      </c>
+      <c r="T6" s="8">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7">
+        <v>216281000</v>
+      </c>
+      <c r="E7">
+        <v>42003000</v>
+      </c>
+      <c r="F7">
+        <v>1.2519</v>
+      </c>
+      <c r="G7">
         <v>0</v>
       </c>
-      <c r="P5">
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>15.1609553478712</v>
+      </c>
+      <c r="J7">
+        <v>2.30011815675463</v>
+      </c>
+      <c r="K7">
+        <v>4.1430699999999998</v>
+      </c>
+      <c r="L7">
+        <v>2.2282178277333702</v>
+      </c>
+      <c r="M7">
+        <v>23106</v>
+      </c>
+      <c r="N7">
         <v>3</v>
       </c>
-      <c r="Q5">
+      <c r="O7">
+        <v>3</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>7</v>
+      </c>
+      <c r="R7">
+        <v>3.5714285714285721</v>
+      </c>
+      <c r="S7" s="9">
+        <v>45.48</v>
+      </c>
+      <c r="T7" s="10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>6.8066413682871403</v>
+      </c>
+      <c r="K8">
+        <v>35.659064999999998</v>
+      </c>
+      <c r="L8">
+        <v>2.75783118188044</v>
+      </c>
+      <c r="M8">
+        <v>29523</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8">
+        <v>2</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>7</v>
+      </c>
+      <c r="R8">
+        <v>3.8571428571428572</v>
+      </c>
+      <c r="S8" s="11">
+        <v>35.42</v>
+      </c>
+      <c r="T8" s="12">
+        <v>79.17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>1447600000</v>
+      </c>
+      <c r="E9">
+        <v>48700000</v>
+      </c>
+      <c r="F9">
+        <v>0.58020000000000005</v>
+      </c>
+      <c r="G9">
+        <v>0.84</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>15.4360565322303</v>
+      </c>
+      <c r="J9">
+        <v>1.3099235926658299</v>
+      </c>
+      <c r="L9">
+        <v>0.25056507322464799</v>
+      </c>
+      <c r="M9">
+        <v>7103</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>2</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>3</v>
+      </c>
+      <c r="R9">
         <v>3.666666666666667</v>
       </c>
-      <c r="R5">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="S5">
-        <v>0.375</v>
-      </c>
-      <c r="T5">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="U5">
-        <v>0.5</v>
-      </c>
-      <c r="V5">
-        <v>0.25</v>
-      </c>
-      <c r="W5">
-        <v>0.5</v>
-      </c>
-      <c r="X5">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="Y5">
-        <v>1</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="4">
-        <v>58.8</v>
+      <c r="S9" s="13">
+        <v>61.38</v>
+      </c>
+      <c r="T9" s="14">
+        <v>86.11</v>
       </c>
     </row>
   </sheetData>
